--- a/artfynd/A 44564-2021 artfynd.xlsx
+++ b/artfynd/A 44564-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 44564-2021 artfynd.xlsx
+++ b/artfynd/A 44564-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>62879346</v>
       </c>
       <c r="B2" t="n">
-        <v>109335</v>
+        <v>109345</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 44564-2021 artfynd.xlsx
+++ b/artfynd/A 44564-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>62879346</v>
       </c>
       <c r="B2" t="n">
-        <v>109345</v>
+        <v>109358</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 44564-2021 artfynd.xlsx
+++ b/artfynd/A 44564-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>62879346</v>
       </c>
       <c r="B2" t="n">
-        <v>109358</v>
+        <v>109359</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 44564-2021 artfynd.xlsx
+++ b/artfynd/A 44564-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>62879346</v>
       </c>
       <c r="B2" t="n">
-        <v>109359</v>
+        <v>109362</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 44564-2021 artfynd.xlsx
+++ b/artfynd/A 44564-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -824,10 +824,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>91170064</v>
+        <v>106915671</v>
       </c>
       <c r="B3" t="n">
-        <v>107338</v>
+        <v>78602</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -836,57 +836,44 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1760</v>
+        <v>6463</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kvällsmaskros</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Taraxacum praestans</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>H. Lindb.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Balketorp, 350 m VSV om, Dls</t>
+          <t>Balketorp, Dls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>332729.2693134078</v>
+        <v>332561.5843902915</v>
       </c>
       <c r="R3" t="n">
-        <v>6498008.683288229</v>
+        <v>6498073.292988635</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -908,14 +895,9 @@
           <t>Färgelanda</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>OD-Fär-0093</t>
-        </is>
-      </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2016-05-30</t>
+          <t>2023-02-22</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -925,7 +907,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2016-05-30</t>
+          <t>2023-02-22</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -943,143 +925,18 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>fuktig stigkant</t>
-        </is>
-      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Claes Kannesten</t>
+          <t>Christine Bryngelsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kjell Eriksson, Ulla Eriksson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>106915671</v>
-      </c>
-      <c r="B4" t="n">
-        <v>78602</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>6463</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Bårdlav</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Nephroma parile</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Balketorp, Dls</t>
-        </is>
-      </c>
-      <c r="Q4" t="n">
-        <v>332561.5843902915</v>
-      </c>
-      <c r="R4" t="n">
-        <v>6498073.292988635</v>
-      </c>
-      <c r="S4" t="n">
-        <v>25</v>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>Västra Götaland</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Färgelanda</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>Dalsland</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>Färgelanda</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2023-02-22</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>2023-02-22</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF4" t="inlineStr"/>
-      <c r="AG4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>Christine Bryngelsson</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
           <t>Christine Bryngelsson, Samuel Sjöberg</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
